--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Allocate</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, ECS, RDS, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3863b07cca34df6</t>
+          <t>https://www.indeed.com/viewjob?jk=53d67e2c6a917d94</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf6ebaa193170fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e3863b07cca34df6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Associate - DevOps Engineer / DevOps Engineer</t>
+          <t>AI Enterprise Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e39bb741b6ed38</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf6ebaa193170fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
+          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39735e72a86863ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7c5ebe00eaa753</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Associate - DevOps Engineer / DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
+          <t>https://www.indeed.com/viewjob?jk=19e39bb741b6ed38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639185415ab38daf</t>
+          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Primerica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
+          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ETL Informatica Developer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6850ff8414aeb49</t>
+          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Upbound Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>ETL Informatica Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d6850ff8414aeb49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Advanced Drainage Systems</t>
+          <t>Upbound Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hilliard, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fa63afaad1ae0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Azure Databricks handson Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vedant Technologies</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e22844d35ce2e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,46 +1077,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e0ecb5d10c6090</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Node)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Vedant Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e22844d35ce2e4d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28a164543501fa9e</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f23c8279b155ead</t>
+          <t>https://www.indeed.com/viewjob?jk=56e0ecb5d10c6090</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Engineering (Databricks)</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Curinos</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer (AWS, Node)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Implementation Solutions Architect</t>
+          <t>Senior Engineer, ML Engineering (Databricks)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Curinos</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
+          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
+          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, YARN, Scala, REST API integration, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb27c1a96af1b03</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Implementation Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Observability</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7798608e6c8e6d0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd483611d5daf4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NYS ITS HBITS Senior IT Specialist</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Oracle, SQL Server, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1457cdbfc218d897</t>
+          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=bd483611d5daf4ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1961,29 +1961,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec07f9df27cc65f</t>
+          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer- Atlanta, GA</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88ad68d887d399c</t>
+          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>Senior DevOps Engineer- Atlanta, GA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=f88ad68d887d399c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jobility</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jobility</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bad4b3cca781fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect (Remote)</t>
+          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, Azure, Vertex AI, Scala, Oracle, SQL Server, DynamoDB</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4082cc434145a52</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>mLabs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+          <t>https://www.indeed.com/viewjob?jk=5bad4b3cca781fe4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Cloud Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Akron, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, ECS, IAM, Azure, Vertex AI, Scala, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe4922b6f5fcc6c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a4082cc434145a52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oracle Data Platform Multi-Cloud Architect</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,157 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Spark, Kafka, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db92aa655f31f542</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Nextech Systems</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>Senior Software Engineer - Cloud Services</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simbex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lebanon, NH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf6ebaa193170fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9529a493965b7b</t>
         </is>
       </c>
     </row>
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
+          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
+          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ETL Informatica Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6850ff8414aeb49</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>ETL Informatica Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Upbound Group</t>
+          <t>Ashra Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
+          <t>https://www.indeed.com/viewjob?jk=d6850ff8414aeb49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Databricks handson Architect</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Upbound Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Azure Databricks handson Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
+          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Head Universal Banker, One California Branch</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>RDS, HDFS, Hive, Sqoop, Impala, Spark, Scala, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1688b5b79437db</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vedant Technologies</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e22844d35ce2e4d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,77 +1186,77 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e0ecb5d10c6090</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Node)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Engineering (Databricks)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Curinos</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Implementation Solutions Architect</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Senior Software Engineer (AWS, Node)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, ML Engineering (Databricks)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Curinos</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>Implementation Solutions Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Scala, PostgreSQL, MySQL, CI/CD, Maven</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd483611d5daf4ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8883e9946b234da5</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer- Atlanta, GA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88ad68d887d399c</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>Enterprise Applications Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>JM Eagle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jobility</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bad4b3cca781fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=8883e9946b234da5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect (Remote)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, Azure, Vertex AI, Scala, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4082cc434145a52</t>
+          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>Jobility</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,15 +2516,540 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Global Partners LP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Urology Centers of Alabama</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Homewood, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SynergenX Health Holdings</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer I</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Axon</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>mLabs</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bad4b3cca781fe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Architect (Remote)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Signet Jewelers</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Akron, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, IAM, Azure, Vertex AI, Scala, Oracle, SQL Server, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4082cc434145a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Integration Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nextech Systems</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
         </is>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer - Cloud Services</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Simbex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lebanon, NH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3863b07cca34df6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9529a493965b7b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Services</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Simbex</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lebanon, NH, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9529a493965b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fab088046f1d5891</t>
         </is>
       </c>
     </row>
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Associate - DevOps Engineer / DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e39bb741b6ed38</t>
+          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Primerica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
+          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Primerica</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
+          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
+          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fitch Ratings</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
+          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Upbound Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ETL Informatica Developer</t>
+          <t>Azure Databricks handson Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ashra Technology</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Informatica PowerCenter, Oracle, SQL Server</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6850ff8414aeb49</t>
+          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Upbound Group</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Databricks handson Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Head Universal Banker, One California Branch</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, HDFS, Hive, Sqoop, Impala, Spark, Scala, MongoDB, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1688b5b79437db</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Software Engineer (AWS, Node)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Senior Engineer, ML Engineering (Databricks)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Curinos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Node)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Engineering (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Curinos</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Implementation Solutions Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,29 +1676,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>API Gateway, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e4cf30b4bd0a5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Implementation Solutions Architect</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,46 +1707,46 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2f3fb5c23b3945</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>mLabs</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bad4b3cca781fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Solutions Architect (Remote)</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, Azure, Vertex AI, Scala, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4082cc434145a52</t>
+          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3015,41 +3015,6 @@
         </is>
       </c>
       <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Nextech Systems</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
         </is>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data / Database Engineer - SQL, Oracle, PL/SQL, Informatica, ETL, Powercenter</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
+          <t>https://www.indeed.com/viewjob?jk=331ee6d2b9af53d4</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>California Coast Credit Union</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
+          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fitch Ratings</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
+          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
+          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Upbound Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Databricks handson Architect</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Upbound Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Azure Databricks handson Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
+          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Specialist, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc9bd01410ee94e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Node)</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Engineering (Databricks)</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Curinos</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Software Engineer (AWS, Node)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, DynamoDB, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c045f1d95301aef</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
+          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Implementation Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70cdcaee06adcf4</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Senior Engineer, ML Engineering (Databricks)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Curinos</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36e132a1cd0c73</t>
+          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer – MHTECHIN (USA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>mhtechin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>API Gateway, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e4cf30b4bd0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>API Gateway, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e4cf30b4bd0a5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2f3fb5c23b3945</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enterprise Applications Architect</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JM Eagle</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>Enterprise Applications Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>JM Eagle</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8883e9946b234da5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
+          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - Capital Markets - NYC / Dallas / Los Angelas</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c58ef4f6c13dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jobility</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
+          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Jobility</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+          <t>Software Engineer - Java and Spring WebFlux</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+          <t>https://www.indeed.com/viewjob?jk=94facea91683e65c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Integration Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Nextech Systems</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,41 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Nextech Systems</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
         </is>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
+          <t>https://www.indeed.com/viewjob?jk=481d923fb039795b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fitch Ratings</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lawrence, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
+          <t>https://www.indeed.com/viewjob?jk=41414a51a1f25bae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13202823e54f41d9</t>
+          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
         </is>
       </c>
     </row>
@@ -893,20 +893,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Databricks</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b2954d105ec3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
         </is>
       </c>
     </row>
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Databricks handson Architect</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=511f86fc1563a9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Specialist, Full-Stack Engineer</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce95c35e291923d6</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc9bd01410ee94e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc9bd01410ee94e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6b715c5b39bb01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Applications Architect</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JM Eagle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Enterprise Applications Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>JM Eagle</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jobility</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Java and Spring WebFlux</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94facea91683e65c</t>
+          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Jobility</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Software Engineer - Java and Spring WebFlux</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+          <t>https://www.indeed.com/viewjob?jk=94facea91683e65c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,15 +2971,120 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Integration Architect</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nextech Systems</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
         </is>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481d923fb039795b</t>
+          <t>https://www.indeed.com/viewjob?jk=26394a63af389d62</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lawrence, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41414a51a1f25bae</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba1ec9e7778b066</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fitch Ratings</t>
+          <t>Master Electronics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Hadoop, Spark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20da1d593ffe4713</t>
+          <t>https://www.indeed.com/viewjob?jk=8c73446a5f5a2ca0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976253ecfe9e19de</t>
+          <t>https://www.indeed.com/viewjob?jk=481d923fb039795b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Lawrence, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
+          <t>https://www.indeed.com/viewjob?jk=41414a51a1f25bae</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Upbound Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Upbound Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Engineer – Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6b715c5b39bb01</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Python Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6b715c5b39bb01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Node)</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,112 +1501,112 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdb739be063e00a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>AI/ML Solutions Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (AWS, Node)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Engineering (Databricks)</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Curinos</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer – MHTECHIN (USA)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>mhtechin</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,77 +1711,77 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>API Gateway, Scala, Oracle, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e4cf30b4bd0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Senior Engineer, ML Engineering (Databricks)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Curinos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
+          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Software Engineer – MHTECHIN (USA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>mhtechin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Crider Foods</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Stillmore, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Applications Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JM Eagle</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Enterprise Applications Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>JM Eagle</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
+          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d677323b8f1a2636</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b36799dfc012672</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Remote Data Engineer - &amp; Modeler Informatica</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a88f61dc550d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8883e9946b234da5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435f09808948c67f</t>
+          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jobility</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Java and Spring WebFlux</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, CI/CD, Maven, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94facea91683e65c</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Jobility</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Data Scientist - Optimization</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>IT Enterprise Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Integration Architect</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79af0156b1e69d17</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer in Test – Performance Testing (Remote - US)</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nextech Systems</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,262 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ece1679bb1b68d39</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Integration Architect</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data / Database Engineer - SQL, Oracle, PL/SQL, Informatica, ETL, Powercenter</t>
+          <t>Penetration Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331ee6d2b9af53d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2d7835a40e0de0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data / Database Engineer - SQL, Oracle, PL/SQL, Informatica, ETL, Powercenter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primerica</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
+          <t>https://www.indeed.com/viewjob?jk=331ee6d2b9af53d4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California Coast Credit Union</t>
+          <t>Primerica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Snowflake, SQL Server, MySQL, MongoDB, NoSQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19e3275d263cd408</t>
+          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f5c842f42b9fab</t>
+          <t>https://www.indeed.com/viewjob?jk=4952bffe58e2575f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer IV</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Upbound Group</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake</t>
+          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f96ecf719dda765</t>
+          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Google Cloud Native Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc9bd01410ee94e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc9bd01410ee94e</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>Cloud Database Administrator, Sr.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=e485e5057086c57b</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, BigQuery, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0caaaf2a7e72b6eb</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Python Data Engineer</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6b715c5b39bb01</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f54c187f37e51c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdb739be063e00a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>AI/ML Solutions Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,112 +1501,112 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdb739be063e00a</t>
+          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AWS, Node)</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7fbe872d043151b</t>
+          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
+          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Data Analytics Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Crider Foods</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Stillmore, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – MHTECHIN (USA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>mhtechin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Engineering (Databricks)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Curinos</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, Delta Live Tables, YARN, Spark, Scala, ELT, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12981bc42f8d0ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer – MHTECHIN (USA)</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>mhtechin</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
+          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analytics Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Crider Foods</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stillmore, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - J2EE/Spring Boot</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Angular Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
+          <t>Enterprise Applications Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JM Eagle</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Applications Architect</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JM Eagle</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>BI Engineer - Data Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
+          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
+          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
+          <t>https://www.indeed.com/viewjob?jk=a6eb4884631c4944</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Business Analyst, Senior Associate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>DevOps Engineering Intern</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Senior Product Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8883e9946b234da5</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5010db1afd8a4a00</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Scientist - Optimization</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598b7862841558a5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>IT Enterprise Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
+          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jobility</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1690dbadbec022c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist - Optimization</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
+          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Enterprise Architect</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
+          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,262 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>NCSA College Recruiting</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>IMG Academy</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer, Marketing</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>IMG Academy</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Earth City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Integration Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Dimensional Modeling, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cd2537dc81bb4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Simbex</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lebanon, NH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9529a493965b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=e477d5aaf587262c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Snowflake Architect - DBT and Cortex AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab088046f1d5891</t>
+          <t>https://www.indeed.com/viewjob?jk=aed7e6578e3c4d9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
+          <t>https://www.indeed.com/viewjob?jk=fab088046f1d5891</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7c5ebe00eaa753</t>
+          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Penetration Tester</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2d7835a40e0de0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7c5ebe00eaa753</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data / Database Engineer - SQL, Oracle, PL/SQL, Informatica, ETL, Powercenter</t>
+          <t>Penetration Tester</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331ee6d2b9af53d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2d7835a40e0de0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data / Database Engineer - SQL, Oracle, PL/SQL, Informatica, ETL, Powercenter</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Primerica</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
+          <t>https://www.indeed.com/viewjob?jk=331ee6d2b9af53d4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Primerica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f05d2b3593772f33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>American Heart Association</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Township of Jackson, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Hadoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26394a63af389d62</t>
+          <t>https://www.indeed.com/viewjob?jk=a03496283ad3b0d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Application Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>SynergenX Health Holdings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ba1ec9e7778b066</t>
+          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Master Electronics</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Township of Jackson, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Hadoop, Spark, Scala, ELT, MLOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c73446a5f5a2ca0</t>
+          <t>https://www.indeed.com/viewjob?jk=26394a63af389d62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Java Application Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481d923fb039795b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba1ec9e7778b066</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Alarm.com</t>
+          <t>Master Electronics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lawrence, KS, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Hadoop, Spark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41414a51a1f25bae</t>
+          <t>https://www.indeed.com/viewjob?jk=8c73446a5f5a2ca0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4952bffe58e2575f</t>
+          <t>https://www.indeed.com/viewjob?jk=481d923fb039795b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Alarm.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lawrence, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e852f89aa147a38</t>
+          <t>https://www.indeed.com/viewjob?jk=41414a51a1f25bae</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Google Cloud Native Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pediatric Associates Family of Companies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Pedro, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc9bd01410ee94e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1995eaa448212</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>Agentic AI Data Engineer - CMC Data Integration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=39a6a17108976060</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator, Sr.</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e485e5057086c57b</t>
+          <t>https://www.indeed.com/viewjob?jk=4952bffe58e2575f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Data Engineer – Platform &amp; Analytics</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=72543b6e05cc0162</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Database Administrator, Sr.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=e485e5057086c57b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Engineer – Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,129 +1336,129 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Hadoop, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdb739be063e00a</t>
+          <t>https://www.indeed.com/viewjob?jk=e033630afa658f8c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
+          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Sr. Cloud Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b090e1238aa6584f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>R&amp;D Cloud Engineering Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,172 +1581,172 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81130977825ed1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Vedan Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f7dd9d12dec5e95</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdb739be063e00a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics Developer</t>
+          <t>AI/ML Solutions Architect - PostgreSQL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Crider Foods</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stillmore, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d883bc65769a81</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer – MHTECHIN (USA)</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mhtechin</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>OFFICE HOURS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
+          <t>https://www.indeed.com/viewjob?jk=af024982951791dc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
+          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,207 +1931,207 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd8de92e982af67</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=87615fc3fda41da1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce6e57ea03bfddf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer – MHTECHIN (USA)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>mhtechin</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,94 +2141,94 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b802a7acff1d5ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - J2EE/Spring Boot</t>
+          <t>Data Analytics Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crider Foods</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stillmore, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, HDFS, Spark, Scala, Kafka, Cassandra, NoSQL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea46fe6dc4046714</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Angular Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8a6f2b73f1fc2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enterprise Applications Architect</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JM Eagle</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Power BI, Tableau, CI/CD</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d392d906a4f4d8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>Acquire-Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>BehaviorSpan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BI Engineer - Data Analytics</t>
+          <t>Data Engineer - Oracle data integrato and BI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Oracle, ETL, ELT, Power BI, Tableau, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2771eb078ba01ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (CHARLOTTE, NC)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6eb4884631c4944</t>
+          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Business Analyst, Senior Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, Tableau, Git</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0e3fa860fcbe7e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3c1a2d78dbef72</t>
+          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,147 +2551,147 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MongoDB, DynamoDB, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc5c72de81426773</t>
+          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>IT System Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>cyber technology innovations</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, CloudWatch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=70eeb725c73e2eb3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist - Optimization</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT Enterprise Architect</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a6eb4884631c4944</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior Site Reliability Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Discogs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, S3, RDS, Kafka, Kafka Connect, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a924459fc3278a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
+          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Finance Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Databricks, BigQuery, Snowflake, Oracle, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc59d1bea902c70f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Engineer III - Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+          <t>https://www.indeed.com/viewjob?jk=92f1cdeea67d5c58</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Data Scientist - Optimization</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>IT Enterprise Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,15 +3076,330 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Edward Jones</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
         </is>

--- a/results/job_matches_2026-07-09.xlsx
+++ b/results/job_matches_2026-07-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Snowflake Architect - DBT and Cortex AI</t>
+          <t>Senior Data Engineer (Hybrid, Houston based)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>RectorSeal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed7e6578e3c4d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=56bf46bcdf3a7d3e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Snowflake Architect - DBT and Cortex AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab088046f1d5891</t>
+          <t>https://www.indeed.com/viewjob?jk=aed7e6578e3c4d9c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
+          <t>https://www.indeed.com/viewjob?jk=fab088046f1d5891</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Databricks, Unity Catalog, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7c5ebe00eaa753</t>
+          <t>https://www.indeed.com/viewjob?jk=33d347250384414c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Penetration Tester</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, API Gateway, RDS, Databricks, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2d7835a40e0de0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7c5ebe00eaa753</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer/ Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SynergenX Health Holdings</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae3f933ced0782ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a62b0f3021eecff3</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Management Business Systems Analyst Senior</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>AmeriHealth Caritas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72543b6e05cc0162</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe8b4359c9f57e8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator, Sr.</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e485e5057086c57b</t>
+          <t>https://www.indeed.com/viewjob?jk=72543b6e05cc0162</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Data Engineer – Platform &amp; Analytics</t>
+          <t>Cloud Database Administrator, Sr.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e485e5057086c57b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
+          <t>AI Data Engineer – Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Athena, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
+          <t>https://www.indeed.com/viewjob?jk=e7544b63dae902ba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer- Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
+          <t>https://www.indeed.com/viewjob?jk=843e1428f95c6703</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ProCare solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
+          <t>https://www.indeed.com/viewjob?jk=05d26e9d276de69c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e03f61f231e6f7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ProCare solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, Azure, GCP, Scala, SQL Server</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59621637da2df488</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3d7f6b293b8798</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Kafka, Snowflake, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e033630afa658f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9c60c8af1cd2657</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IGT</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
+          <t>https://www.indeed.com/viewjob?jk=e033630afa658f8c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Cloud Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>IGT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b090e1238aa6584f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccfeb0ae91c8b22c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R&amp;D Cloud Engineering Scientist</t>
+          <t>Sr. Cloud Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef81130977825ed1</t>
+          <t>https://www.indeed.com/viewjob?jk=b090e1238aa6584f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>R&amp;D Cloud Engineering Scientist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vedan Technologies</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f7dd9d12dec5e95</t>
+          <t>https://www.indeed.com/viewjob?jk=ef81130977825ed1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vedan Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f7dd9d12dec5e95</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
+          <t>Data Infrastructure Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
+          <t>https://www.indeed.com/viewjob?jk=5b2d6340b7dbd35b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Software Engineer-Tech Ex AI Assets Foundry Team</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OFFICE HOURS</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af024982951791dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0b83db5488d77940</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>OFFICE HOURS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, Scala, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
+          <t>https://www.indeed.com/viewjob?jk=af024982951791dc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Scala, DynamoDB, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
+          <t>https://www.indeed.com/viewjob?jk=1137912cd4930b5c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c279a3c045a08727</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
+          <t>https://www.indeed.com/viewjob?jk=3044d3acb77883ad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, Athena, RDS, Databricks, Medallion Architecture, Spark, PySpark, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
+          <t>https://www.indeed.com/viewjob?jk=92c4474967707e83</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bd8de92e982af67</t>
+          <t>https://www.indeed.com/viewjob?jk=b13e9ac170037a33</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87615fc3fda41da1</t>
+          <t>https://www.indeed.com/viewjob?jk=12e8643c707d53bb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce6e57ea03bfddf</t>
+          <t>https://www.indeed.com/viewjob?jk=4bd8de92e982af67</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer – MHTECHIN (USA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mhtechin</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Scala, Snowflake, Oracle, Data Modeling, ETL, Jenkins, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
+          <t>https://www.indeed.com/viewjob?jk=87615fc3fda41da1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b802a7acff1d5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce6e57ea03bfddf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Software Engineer – MHTECHIN (USA)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>mhtechin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
+          <t>https://www.indeed.com/viewjob?jk=b83f09563e0a3d38</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analytics Developer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crider Foods</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stillmore, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,77 +2201,77 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
+          <t>https://www.indeed.com/viewjob?jk=8b802a7acff1d5ad</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe4d9a822bce57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Python AI Engineer</t>
+          <t>Data Analytics Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crider Foods</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Stillmore, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, SQL Server, ETL, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4013e80d3a58db</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Contract</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c71baf7b7eedd7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brook INC</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8ebe939dba44ab</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Acquire-Site Reliability Engineer</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BehaviorSpan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SNS, ECS, IAM, RDS, Scala, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>Kafka, PostgreSQL, ETL, CI/CD, Jenkins, Maven, Docker, Jenkins, pytest, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccf8a44263a0130</t>
+          <t>https://www.indeed.com/viewjob?jk=6e793e39138e9c31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrato and BI</t>
+          <t>Senior Cloud Engineer - Contract</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea82fd770b87f655</t>
+          <t>https://www.indeed.com/viewjob?jk=df19e7dbad1a512f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Brook INC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Kinesis, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, dbt, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c645cbff1d3870</t>
+          <t>https://www.indeed.com/viewjob?jk=d754b9ca64323d6e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24d0af560e9bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9885cdd8f6f0e5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b21a772800827417</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98424ae5c6548f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer - FDE - Digital Native Business</t>
+          <t>IT System Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>cyber technology innovations</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, CloudWatch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43640f8dedff80ae</t>
+          <t>https://www.indeed.com/viewjob?jk=70eeb725c73e2eb3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, Hive, Spark, Scala, DataOps</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f2d5502617e455</t>
+          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT System Engineer</t>
+          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>cyber technology innovations</t>
+          <t>AlixPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, SQL Server, MySQL, CloudWatch</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70eeb725c73e2eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Insights &amp; Analytics Senior Data Engineer (Contract)</t>
+          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (CHARLOTTE, NC)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AlixPartners</t>
+          <t>Compass Group USA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,77 +2691,77 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e3a4117d82354a9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6eb4884631c4944</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Salas O'Brien</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139ae06dd742f9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4a147881279cc0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SENIOR DEVELOPER, BUSINESS INTELLIGENCE &amp; PROJECTS (CHARLOTTE, NC)</t>
+          <t>Senior Site Reliability Engineer (REMOTE)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Compass Group USA</t>
+          <t>Discogs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, S3, RDS, Kafka, Kafka Connect, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6eb4884631c4944</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a924459fc3278a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (REMOTE)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Discogs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, Kafka Connect, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a924459fc3278a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Urology Centers of Alabama</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Homewood, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e936a38ae1e760a</t>
+          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Urology Centers of Alabama</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Homewood, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Snowflake, Oracle, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61588a41f9c88e4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc59d1bea902c70f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, Flink) | Berkeley Heights, NJ (5 Days Onsite) | Contract W2 only</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff199be74bdba33</t>
+          <t>https://www.indeed.com/viewjob?jk=92f1cdeea67d5c58</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Finance Systems Integration Engineer</t>
+          <t>Data Scientist - Optimization</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Snowflake, Oracle, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc59d1bea902c70f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/AWS</t>
+          <t>IT Enterprise Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=886d622b68bd75e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Operational Data &amp; Observability Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Oracle, ETL, ELT, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Splunk, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92f1cdeea67d5c58</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a5446b79f2284f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist - Optimization</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, MLOps, Git, Python, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d14e0caa3293192</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT Enterprise Architect</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>NCSA College Recruiting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94b4fce819533c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
+          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Fullstack Engineer, Marketing</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>IMG Academy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
+          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f56162e38c2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NCSA College Recruiting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c291169defa77d17</t>
+          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Software Engineer 2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362edf60a4890cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Fullstack Engineer, Marketing</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IMG Academy</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442d3e11f0a53f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e65e864080e6f228</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, MongoDB, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,77 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bee7f3b1d3558f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5331edf6c905499e</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer 2</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Earth City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3b8341850dde41</t>
+          <t>https://www.indeed.com/viewjob?jk=379a672460ecff73</t>
         </is>
       </c>
     </row>
